--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plantilla-proveedores-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plantilla-proveedores-parrillero-asador-eventos.xlsx
@@ -19,7 +19,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Captacion B2B planners y age" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Hosply.pro · directorio HOR" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'1. Carniceria mayorista'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'2. Carbon, leña y combustible'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'3. Equipamiento parrilla y asad'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'4. Cuchilleria, tablas, menaje '!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'5. Vajilla, cuberteria, mantele'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'6. Indumentaria y proteccion'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'7. Seguros, gestoria y asesoria'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'8. Transporte y vehiculos event'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'9. Captacion B2B planners y age'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'10. Hosply.pro · directorio HOR'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -493,9 +504,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -518,6 +529,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -691,13 +703,30 @@
         <v>93</v>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/plan-negocio-parrillero-asador-eventos · info@aichef.pro</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -705,7 +734,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -734,6 +763,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1169,7 +1199,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1177,7 +1216,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1206,6 +1245,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1449,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1417,7 +1466,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1446,6 +1495,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1953,7 +2003,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1961,7 +2020,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1990,6 +2049,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2383,7 +2443,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2391,7 +2460,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2420,6 +2489,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2973,7 +3043,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2981,7 +3060,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3010,6 +3089,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3403,7 +3483,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3411,7 +3500,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3440,6 +3529,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3875,7 +3965,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3883,7 +3982,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3912,6 +4011,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4271,7 +4371,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4279,7 +4388,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4308,6 +4417,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4739,7 +4849,16 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4747,7 +4866,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4776,6 +4895,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5131,6 +5251,15 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>